--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +945,123 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120517058</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bostället, Bostället, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>363123</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6622195</v>
+      </c>
+      <c r="S4" t="n">
+        <v>19</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Precis norr om jaktställningen. 3 individer.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1062,137 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120594284</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bostället, Bostället, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>363033</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6622192</v>
+      </c>
+      <c r="S5" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inte helt säker på artbestämning. Området ska avverkas. Det bör göras en grundlig inventering!</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>120855067</v>
       </c>
       <c r="B6" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>121343135</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1317,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343135</v>
+        <v>121342836</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,6 +1422,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1320,7 +1320,7 @@
         <v>121342836</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1440,6 +1440,131 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121489161</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98094</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lerbäcken, 250 m SSV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>363006</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6622194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>S-Arv-0529</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121342836</v>
+        <v>121343135</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,11 +1422,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1446,7 +1441,7 @@
         <v>121489161</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343135</v>
+        <v>121342836</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,6 +1422,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1441,7 +1446,7 @@
         <v>121489161</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>121342836</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>121489161</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>121342836</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>121489161</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1317,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121342836</v>
+        <v>121343135</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,11 +1422,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1317,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343135</v>
+        <v>121342836</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,6 +1422,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121342836</v>
+        <v>121343135</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,11 +1422,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1446,7 +1441,7 @@
         <v>121489161</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -1418,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>

--- a/artfynd/A 62900-2023 artfynd.xlsx
+++ b/artfynd/A 62900-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3061294</v>
+        <v>120594284</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lerbäcken, 250 m SSV om, Vrm</t>
+          <t>Bostället, Bostället, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363005.4526455301</v>
+        <v>363033</v>
       </c>
       <c r="R2" t="n">
-        <v>6622223.683358983</v>
+        <v>6622192</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-04-06</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-04-06</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 275 bladrosetter med 268 fröställningar, spridd från 097-666 norrut till 270-651</t>
+          <t>Inte helt säker på artbestämning. Området ska avverkas. Det bör göras en grundlig inventering!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,87 +781,92 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre granskog med inslag av tall</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Larsson, Elvi Eriksson</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3061293</v>
+        <v>120921742</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandbäcken, 200 m V-VSV om, Vrm</t>
+          <t>Sandbäcken, Sandbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363163.3667446831</v>
+        <v>363242</v>
       </c>
       <c r="R3" t="n">
-        <v>6622005.80228304</v>
+        <v>6621990</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,27 +890,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-04-06</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-04-06</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>280 bladrosetter med 63 fröställningar i fem grupper från 946-822 till 988-806</t>
+          <t>Äldre fruktkropp av orange (kork) taggsvampen. Den oranga fruktköttet syns tydligt. Ett exemplar hittat i skogspartiet ganska nära vägen och huset, gran skog med sumpiga partier.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,87 +922,73 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre granskog med inslag av tall</t>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Larsson, Elvi Eriksson</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120594284</v>
+        <v>120517058</v>
       </c>
       <c r="B4" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bostället, Bostället, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363033</v>
+        <v>363123</v>
       </c>
       <c r="R4" t="n">
-        <v>6622192</v>
+        <v>6622195</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,12 +1027,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inte helt säker på artbestämning. Området ska avverkas. Det bör göras en grundlig inventering!</t>
+          <t>Precis norr om jaktställningen. 3 individer.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,68 +1043,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120517058</v>
+        <v>120855067</v>
       </c>
       <c r="B5" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1128,13 +1094,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363123</v>
+        <v>363204</v>
       </c>
       <c r="R5" t="n">
-        <v>6622195</v>
+        <v>6622045</v>
       </c>
       <c r="S5" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1158,27 +1124,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Precis norr om jaktställningen. 3 individer.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,15 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120855067</v>
+        <v>120855293</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,16 +1177,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>206046</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1241,14 +1197,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bostället, Bostället, Vrm</t>
+          <t>Sandbäcken, Sandbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363204</v>
+        <v>363173</v>
       </c>
       <c r="R6" t="n">
-        <v>6622045</v>
+        <v>6622149</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1280,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,7 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Älgspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,15 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121342836</v>
+        <v>3061293</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1308,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1362,17 +1318,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bostället, Bostället, Vrm</t>
+          <t>Sandbäcken, 200 m V-VSV om, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362996</v>
+        <v>363163</v>
       </c>
       <c r="R7" t="n">
-        <v>6622194</v>
+        <v>6622006</v>
       </c>
       <c r="S7" t="n">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1396,62 +1352,57 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2012-04-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2012-04-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>280 bladrosetter med 63 fröställningar i fem grupper från 946-822 till 988-806</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>äldre granskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Per Larsson, Elvi Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121489161</v>
+        <v>3061294</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,12 +1429,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1492,13 +1443,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363006</v>
+        <v>363005</v>
       </c>
       <c r="R8" t="n">
-        <v>6622194</v>
+        <v>6622224</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1520,19 +1471,19 @@
           <t>Arvika</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>S-Arv-0529</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2012-04-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2012-04-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 275 bladrosetter med 268 fröställningar, spridd från 097-666 norrut till 270-651</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,23 +1495,154 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>äldre granskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
+          <t>Per Larsson, Elvi Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3061297</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lerbäcken, 250 m SSV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>363006</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6622194</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>S-Arv-0529</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-04-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-04-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 275 bladrosetter med 268 fröställningar, spridd från 097-666 norrut till 270-651</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre granskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Värmland Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elvi Eriksson, Per Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
